--- a/2_Raw_Data/2_2_BTS_code/BTS_key_words_code_final.xlsx
+++ b/2_Raw_Data/2_2_BTS_code/BTS_key_words_code_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuwe\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liuwe\Desktop\大团队科学样本代表性\BTS_Sample_Stage1_RR\BTS_Sample_Stage1_RR\2_Raw_Data\2_1_TPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33757493-CD9F-48C1-AF21-3E3189C6CF14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA72CA4C-DF13-46D2-9D3A-D36572452C09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="19392" windowHeight="11472" xr2:uid="{D65725F8-0F32-408D-940F-7254C93BA44D}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="220">
   <si>
     <t>ID</t>
   </si>
@@ -481,15 +481,6 @@
     <t>The general fault in our fault lines</t>
   </si>
   <si>
-    <t>Sirota, Miroslav; 艩rol, Jakub; Lisi, Matteo; Juanchich, Marie; Wolfe, Kelly; Buchanan, Erin M.</t>
-  </si>
-  <si>
-    <t>22Mapping and Increasing Error Correction Behaviour in a Culturally Diverse Sample</t>
-  </si>
-  <si>
-    <t>Error Correction, Intuitive Reasoning, Cultural Diversity, Feedback, Justification</t>
-  </si>
-  <si>
     <t>Sorokowski, Piotr; Kowal, Marta; Sternberg, Robert J.; Aavik, Toivo; Akello, Grace; Alhabahba, Mohammad Madallh; Alm, Charlotte; Amjad, Naumana; Anjum, Afifa; Asao, Kelly; Atama, Chiemezie S.; Atamt眉rk Duyar, Derya; Ayebare, Richard; Conroy-Beam, Daniel; Bendixen, Mons; Bensafia, Aicha; Bizumic, Boris; Boussena, Mahmoud; Buss, David M.; Butovskaya, Marina; Can, Seda; Carrier, Antonin; Cetinkaya, Hakan; Croy, Ilona; Cueto, Rosa Mar铆a; Czub, Marcin; Dronova, Daria; Dural, Seda; Duyar, Izzet; Ertugrul, Berna; Espinosa, Agust铆n; Estevan, Ignacio; Esteves, Carla Sofia; Frackowiak, Tomasz; Gardu帽o, Jorge Contreras; Gonz谩lez, Karina Ugalde; Guemaz, Farida; Halamov谩, M谩ria; Herak, Iskra; Horvat, Marina; Hromatko, Ivana; Hui, Chin-Ming; Jaafar, Jas Laile; Jiang, Feng; Kafetsios, Konstantinos; Kav膷i膷, Tina; Kennair, Leif Edward Ottesen; Kervyn, Nicolas; Ha, Truong Thi Khanh; Khilji, Imran Ahmed; K枚bis, Nils C.; Kostic, Aleksandra; Lan, Hoang Moc; L谩ng, Andr谩s; Lennard, Georgina R.; Le贸n, Ernesto; Lindholm, Torun; Linh, Trinh Thi; Lopez, Giulia; Van Luot, Nguyen; Mailhos, Alvaro; Manesi, Zoi; Martinez, Rocio; McKerchar, Sarah L.; Mesk贸, Norbert; Peji膷i膰, Marija; Misra, Girishwar; Monaghan, Conal; Mora, Emanuel C.; Moya-Gar贸fano, Alba; Musil, Bojan; Natividade, Jean Carlos; Nizharadze, George; Oberzaucher, Elisabeth; Oleszkiewicz, Anna; Omar-Fauzee, Mohd Sofian; Onyishi, Ike E.; 脰zener, Baris; Pagani, Ariela Francesca; Pakalniskiene, Vilmante; Parise, Miriam; Pazhoohi, Farid; Pisanski, Annette; Pisanski, Katarzyna; Ponciano, Edna; Popa, Camelia; Prokop, Pavol; Rizwan, Muhammad; Sainz, Mario; Salki膷evi膰, Svjetlana; Sargautyte, Ruta; Sarm谩ny-Schuller, Ivan; Schmehl, Susanne; Shahid, Anam; Sharad, Shivantika; Siddiqui, Razi Sultan; Simonetti, Franco; Tadinac, Meri; Vauclair, Christin-Melanie; Vega, Luis Diego; Walter, Kathryn V.; Widarini, Dwi Ajeng; Yoo, Gyesook; Za钮kov谩, Marta; Zupan膷i膷, Maja; Sorokowska, Agnieszka</t>
   </si>
   <si>
@@ -532,189 +523,191 @@
     <t>Terry, Jenny; Ross, Robert M.; Nagy, Tam谩s; Salgado, Mauricio; Garrido-V谩squez, Patricia; Sarfo, Jacob O.; Cooper, Susan; Buttner, Anke C.; Lima, Tiago J. S.; 脰zt眉rk, 陌brahim; Akay, Nazl谋; Santos, Flavia H.; Artemenko, Christina; Copping, Lee T.; Elsherif, Mahmoud M.; Milovanovi膰, Ilija; Cribbie, Robert A.; Drushlyak, Marina G.; Swainston, Katherine; Shou, Yiyun; Leong贸mez, Juan David; Palena, Nicola; Abidin, Fitri A.; Reyes-Rodr铆guez, Maria F.; He, Yunfeng; Abraham, Juneman; Vatakis, Argiro; Jankowsky, Kristin; Schmidt, Stephanie N. L.; Grimm, Elise; Gonz谩lez, Desir茅e; Schmid, Philipp; Ferreira, Roberto A.; Rozgonjuk, Dmitri; 脰zhan, Neslihan; O鈥機onnor, Patrick A.; Zsido, Andras N.; Stiglic, Gregor; Rhodes, Darren; Rodr铆guez, Cristina; Ropovik, Ivan; Enea, Violeta; Nurwanti, Ratri; Estudillo, Alejandro J.; Beribisky, Nataly; Himawan, Karel K.; Geven, Linda M.; Hoogmoed, Anne H. van; Bret, Am茅lie; Chapman, Jodie E.; Alter, Udi; Flack, Zoe M.; Hanna, Donncha; Soltanlou, Mojtaba; Banik, Gabriel; Adamkovi膷, Mat煤拧; Ven, Sanne H. G. van der; Mosbacher, Jochen A.; 艦en, Hilal H.; Anderson, Joel R.; Batashvili, Michael; Groot, Kristel de; Parker, Matthew O.; Helmy, Mai; Ostroha, Mariia M.; Gilligan-Lee, Katie A.; Egara, Felix O.; Barwood, Martin J.; Thomas, Karuna; McMahon, Grace; Griffin, Siobh谩n M.; Nuerk, Hans-Christoph; Counsell, Alyssa; Lindemann, Oliver; Rooy, Dirk Van; Wege, Theresa E.; Lewis, Joanna E.; Aczel, Balazs; Monaghan, Conal; Al-Hoorie, Ali H.; Huber, Julia F.; Yapan, Saadet; V谩squez, Mauricio E. Garrido; Callea, Antonino; Ergiyen, Tolga; Clay, James M.; Mertens, Gaetan; Top莽u, Feyza; Tutlu, Merve G.; T盲ht, Karin; Mikkor, Kristel; Caso, Letizia; Karner, Alexander; Storm, Maxine M. C.; Daroczy, Gabriella; Zein, Rizqy A.; Greco, Andrea; Buchanan, Erin M.; Schmid, Katharina; Hunt, Thomas E.; Keersmaecker, Jonas De; Branney, Peter E.; Randell, Jordan; Clark, Oliver J.; Steltenpohl, Crystal N.; Malu, Bhasker; Teke艧, Burcu; Ramis, TamilSelvan; Agrigoroaei, Stefan; Badcock, Nicholas A.; McAloney-Kocaman, Kareena; Semenikhina, Olena V.; Graf, Erich W.; Lea, Charlie; Ogba, Kalu T. U.; Guppy, Fergus M.; Warhurst, Amy C.; Lindsay, Shane; Khateeb, Ahmed Al; Scharnowski, Frank; Kwaadsteniet, Leontien de; Francis, Kathryn B.; Lecompte, Mariah; Webster, Lisa A. D.; Morsanyi, Kinga; Forwood, Suzanna E.; Walters, Elizabeth R.; Tip, Linda K.; Wagge, Jordan R.; Lai, Ho Yan; Crossland, Deborah S.; Darda, Kohinoor M.; Flack, Tessa R.; Leviston, Zoe; Brolly, Matthew; Hills, Samuel P.; Collins, Elizabeth; Roberts, Andrew J.; Cheung, Wing-Yee; Leonard, Sophie; Verschuere, Bruno; Stanley, Samantha K.; Xenidou-Dervou, Iro; Ghasemi, Omid; Liew, Timothy; Ansari, Daniel; Guilaran, Johnrev; Penny, Samuel G.; Bahnmueller, Julia; Hand, Christopher J.; Rahajeng, Unita W.; Peterburg, Dar; Takacs, Zsofia K.; Platow, Michael J.; Field, Andy P.</t>
   </si>
   <si>
+    <t>The ManyBabies Consortium</t>
+  </si>
+  <si>
+    <t>Quantifying Sources of Variability in Infancy Research Using the Infant-Directed-Speech Preference</t>
+  </si>
+  <si>
+    <t>language acquisition, speech perception, infant-directed speech, reproducibility, experimental methods, open data, open materials, preregistered</t>
+  </si>
+  <si>
+    <t>Tybur, Joshua M.; Inbar, Yoel; Aar酶e, Lene; Barclay, Pat; Barlow, Fiona Kate; de Barra, M铆che谩l; Becker, D. Vaughn; Borovoi, Leah; Choi, Incheol; Choi, Jong An; Consedine, Nathan S.; Conway, Alan; Conway, Jane Rebecca; Conway, Paul; Adoric, Vera Cubela; Demirci, Dilara Ekin; Fern谩ndez, Ana Mar铆a; Ferreira, Diogo Conque Seco; Ishii, Keiko; Jak拧i膰, Ivana; Ji, Tingting; van Leeuwen, Florian; Lewis, David M. G.; Li, Norman P.; McIntyre, Jason C.; Mukherjee, Sumitava; Park, Justin H.; Pawlowski, Boguslaw; Petersen, Michael Bang; Pizarro, David; Prodromitis, Gerasimos; Prokop, Pavol; Rantala, Markus J.; Reynolds, Lisa M.; Sandin, Bonifacio; Sevi, Bari艧; De Smet, Delphine; Srinivasan, Narayanan; Tewari, Shruti; Wilson, Cameron; Yong, Jose C.; 沤e啪elj, Iris</t>
+  </si>
+  <si>
+    <t>Parasite stress and pathogen avoidance relate to distinct dimensions of political ideology across 30 nations</t>
+  </si>
+  <si>
+    <t>political ideology, pathogens, disgust, culture, evolutionary psychology</t>
+  </si>
+  <si>
+    <t>Van Bavel, Jay J.; Cichocka, Aleksandra; Capraro, Valerio; Sj氓stad, Hallgeir; Nezlek, John B.; Pavlovi膰, Tomislav; Alfano, Mark; Gelfand, Michele J.; Azevedo, Flavio; Birtel, Mich猫le D.; Cislak, Aleksandra; Lockwood, Patricia L.; Ross, Robert Malcolm; Abts, Koen; Agadullina, Elena; Aruta, John Jamir Benzon; Besharati, Sahba Nomvula; Bor, Alexander; Choma, Becky L.; Crabtree, Charles David; Cunningham, William A.; De, Koustav; Ejaz, Waqas; Elbaek, Christian T.; Findor, Andrej; Flichtentrei, Daniel; Franc, Renata; Gjoneska, Biljana; Gruber, June; Gualda, Estrella; Horiuchi, Yusaku; Huynh, Toan Luu Duc; Ibanez, Agustin; Imran, Mostak Ahamed; Israelashvili, Jacob; Jasko, Katarzyna; Kantorowicz, Jaroslaw; Kantorowicz-Reznichenko, Elena; Krouwel, Andr茅; Laakasuo, Michael; Lamm, Claus; Leygue, Caroline; Lin, Ming-Jen; Mansoor, Mohammad Sabbir; Marie, Antoine; Mayiwar, Lewend; Mazepus, Honorata; McHugh, Cillian; Minda, John Paul; Mitkidis, Panagiotis; Olsson, Andreas; Otterbring, Tobias; Packer, Dominic J.; Perry, Anat; Petersen, Michael Bang; Puthillam, Arathy; Ria帽o-Moreno, Juli谩n C.; Rothmund, Tobias; Santamar铆a-Garc铆a, Hernando; Schmid, Petra C.; Stoyanov, Drozdstoy; Tewari, Shruti; Todosijevi膰, Bojan; Tsakiris, Manos; Tung, Hans H.; Umbre葯, Radu G.; Vanags, Edmunds; Vlasceanu, Madalina; Vonasch, Andrew; Yucel, Meltem; Zhang, Yucheng; Abad, Mohcine; Adler, Eli; Akrawi, Narin; Mdarhri, Hamza Alaoui; Amara, Hanane; Amodio, David M.; Antazo, Benedict G.; Apps, Matthew; Ay, F. Ceren; Ba, Mouhamadou Hady; Barbosa, Sergio; Bastian, Brock; Berg, Anton; Bernal-Z谩rate, Maria P.; Bernstein, Michael; Bia艂ek, Micha艂; Bilancini, Ennio; Bogatyreva, Natalia; Boncinelli, Leonardo; Booth, Jonathan E.; Borau, Sylvie; Buchel, Ondrej; Cameron, C. Daryl; Carvalho, Chrissie F.; Celadin, Tatiana; Cerami, Chiara; Chalise, Hom Nath; Cheng, Xiaojun; Cian, Luca; Cockcroft, Kate; Conway, Jane; C贸rdoba-Delgado, Mateo Andres; Crespi, Chiara; Crouzevialle, Marie; Cutler, Jo; Cyprya艅ska, Marzena; Dabrowska, Justyna; Daniels, Michael A.; Davis, Victoria H.; Dayley, Pamala N.; Delouvee, Sylvain; Denkovski, Ognjan; Dezecache, Guillaume; Dhaliwal, Nathan A.; Diato, Alelie B.; Di Paolo, Roberto; Drosinou, Marianna; Dulleck, Uwe; Ekmanis, J膩nis; Ertan, Arhan S.; Etienne, Tom W.; Farhana, Hapsa Hossain; Farkhari, Fahima; Farmer, Harry; Fenwick, Ali; Fidanovski, Kristijan; Flew, Terry; Fraser, Shona; Frempong, Raymond Boadi; Fugelsang, Jonathan A.; Gale, Jessica; Garcia-Navarro, E. Bego帽a; Garladinne, Prasad; Ghajjou, Oussama; Gkinopoulos, Theofilos; Gray, Kurt; Griffin, Siobh谩n M.; Gronfeldt, Bjarki; G眉mren, Mert; Gurung, Ranju Lama; Halperin, Eran; Harris, Elizabeth; Herzon, Volo; Hru拧ka, Matej; Huang, Guanxiong; Hudecek, Matthias F. C.; Isler, Ozan; Jangard, Simon; J酶rgensen, Frederik J.; Kachanoff, Frank; Kahn, John; Dangol, Apsara Katuwal; Keudel, Oleksandra; Koppel, Lina; Koverola, Mika; Kubin, Emily; Kunnari, Anton; Kutiyski, Yordan; Laguna, Oscar; Leota, Josh; Lermer, Eva; Levy, Jonathan; Levy, Neil; Li, Chunyun; Long, Elizabeth U.; Longoni, Chiara; Magli膰, Marina; McCashin, Darragh; Metcalf, Alexander L.; Miklou拧i膰, Igor; El Mimouni, Soulaimane; Miura, Asako; Molina-Paredes, Juliana; Monroy-Fonseca, C茅sar; Morales-Marente, Elena; Moreau, David; Muda, Rafa艂; Myer, Annalisa; Nash, Kyle; Nesh-Nash, Tarik; Nitschke, Jonas P.; Nurse, Matthew S.; Ohtsubo, Yohsuke; Oldemburgo de Mello, Victoria; O鈥橫adagain, Cathal; Onderco, Michal; Palacios-Galvez, M. Soledad; Palom盲ki, Jussi; Pan, Yafeng; Papp, Zs贸fia; P盲rnamets, Philip; Paruzel-Czachura, Mariola; Pavlovi膰, Zoran; Pay谩n-G贸mez, C茅sar; Perander, Silva; Pitman, Michael Mark; Prasad, Rajib; Pyrkosz-Pacyna, Joanna; Rathje, Steve; Raza, Ali; R锚go, Gabriel G.; Rhee, Kasey; Robertson, Claire E.; Rodr铆guez-Pascual, Iv谩n; Saikkonen, Teemu; Salvador-Ginez, Octavio; Sampaio, Waldir M.; Santi, Gaia C.; Santiago-Tovar, Natalia; Savage, David; Scheffer, Julian A.; Sch枚negger, Philipp; Schultner, David T.; Schutte, Enid M.; Scott, Andy; Sharma, Madhavi; Sharma, Pujan; Skali, Ahmed; Stadelmann, David; Stafford, Clara Alexandra; Stanojevi膰, Dragan; Stefaniak, Anna; Sternisko, Anni; Stoica, Agustin; Stoyanova, Kristina K.; Strickland, Brent; Sundvall, Jukka; Thomas, Jeffrey P.; Tingh枚g, Gustav; Torgler, Benno; Traast, Iris J.; Tucciarelli, Raffaele; Tyrala, Michael; Ungson, Nick D.; Uysal, Mete S.; Van Lange, Paul A. M.; van Prooijen, Jan-Willem; van Rooy, Dirk; V盲stfj盲ll, Daniel; Verkoeijen, Peter; Vieira, Joana B.; von Sikorski, Christian; Walker, Alexander Cameron; Watermeyer, Jennifer; Wetter, Erik; Whillans, Ashley; Willardt, Robin; Wohl, Michael J. A.; W贸jcik, Adrian Dominik; Wu, Kaidi; Yamada, Yuki; Yilmaz, Onurcan; Yogeeswaran, Kumar; Ziemer, Carolin-Theresa; Zwaan, Rolf A.; Boggio, Paulo S.</t>
+  </si>
+  <si>
+    <t>National identity predicts public health support during a global pandemic</t>
+  </si>
+  <si>
+    <t>national identity, public health support, COVID-19 pandemic, behavioral science, social identity</t>
+  </si>
+  <si>
+    <t>Ve膰kalov, Bojana; Geiger, Sandra J.; Barto拧, Franti拧ek; White, Mathew P.; Rutjens, Bastiaan T.; van Harreveld, Frenk; Stablum, Federica; Ak谋n, Berkan; Aldoh, Alaa; Bai, Jinhao; Berglund, Frida; Bratina Zimic, Ale拧a; Broyles, Margaret; Catania, Andrea; Chen, Airu; Chorz臋pa, Magdalena; Farahat, Eman; G枚tz, Jakob; Hoter-Ishay, Bat; Jordan, Gesine; Joustra, Siri; Klingebiel, Jonas; Krajnc, 沤iva; Krug, Antonia; Andersen, Thomas Lind; L枚loff, Johanna; Natarajan, Divya; Newman-Oktan, Sasha; Niehoff, Elena; Paerels, Celeste; Papirmeister, Rachel; Peregrina, Steven; Pohl, Felicia; Rems枚, Amanda; Roh, Abigail; Rusyidi, Binahayati; Schmidt, Justus; Shavgulidze, Mariam; Vellinho Nardin, Valentina; Wang, Ruixiang; Warner, Kelly; Wattier, Miranda; Wong, Chloe Y.; Younssi, Mariem; Ruggeri, Kai; van der Linden, Sander</t>
+  </si>
+  <si>
+    <t>A 27-country test of communicating the scientific consensus on climate change</t>
+  </si>
+  <si>
+    <t>Vlasceanu, Madalina; Doell, Kimberly C; Bak-Coleman, Joseph B; Todorova, Boryana; Berkebile-Weinberg, Michael M; Grayson, Samantha J; Patel, Yash; Goldwert, Danielle; Pei, Yifei; Chakroff, Alek; Pronizius, Ekaterina; Constantino, Sara; Morais, Michael J; Schumann, Philipp; Rathje, Steve; Fang, Ke; Aglioti, Salvatore Maria; Alfano, Mark; Alvarado-Yepez, Andy J; Andersen, Ang茅lica; Anseel, Frederik; Apps, Matthew A J; Asadli, Chillar; Awuor, Fonda Jane; Azevedo, Flavio; Basaglia, Piero; B茅langer, Jocelyn J; Berger, Sebastian; Bertin, Paul; Bia艂ek, Micha艂; Bialobrzeska, Olga; Blaya-Burgo, Michelle; Bleize, Dani毛lle N M; B酶, Simen; Boecker, Lea; Boggio, Paulo S; Borau, Sylvie; Bos, Bj枚rn; Bouguettaya, Ayoub; Brauer, Markus; Brick, Cameron; Brik, Tymofii; Briker, Roman; Brosch, Tobias; Buchel, Ondrej; Buonauro, Daniel; Butalia, Radhika; Carvacho, H茅ctor; Chamberlain, Sarah A E; Chan, Hang-Yee; Chow, Dawn; Chung, Dongil; Cian, Luca; Cohen-Eick, Noa; Contreras-Huerta, Luis Sebastian; Contu, Davide; Cristea, Vladimir; Cutler, Jo; D'Ottone, Silvana; Keersmaecker, Jonas De; Delcourt, Sarah; Delouv茅e, Sylvain; Diel, Kathi; Douglas, Benjamin D; Drupp, Moritz A; Dubey, Shreya; Ekmanis, J膩nis; Elbaek, Christian T; Elsherif, Mahmoud; Engelhard, Iris M; Escher, Yannik A; Etienne, Tom W; Farage, Laura; Farias, Ana Rita; Feuerriegel, Stefan; Findor, Andrej; Freira, Lucia; Friese, Malte; Gains, Neil Philip; Gallyamova, Albina; Geiger, Sandra J; Genschow, Oliver; Gjoneska, Biljana; Gkinopoulos, Theofilos; Goldberg, Beth; Goldenberg, Amit; Gradidge, Sarah; Grassini, Simone; Gray, Kurt; Grelle, Sonja; Griffin, Siobh谩n M; Grigoryan, Lusine; Grigoryan, Ani; Grigoryev, Dmitry; Gruber, June; Guilaran, Johnrev; Hadar, Britt; Hahnel, Ulf J J; Halperin, Eran; Harvey, Annelie J; Haugestad, Christian A P; Herman, Aleksandra M; Hershfield, Hal E; Himichi, Toshiyuki; Hine, Donald W; Hofmann, Wilhelm; Howe, Lauren; Huaman-Chulluncuy, Enma T; Huang, Guanxiong; Ishii, Tatsunori; Ito, Ayahito; Jia, Fanli; Jost, John T; Jovanovi膰, Veljko; Jurgiel, Dominika; K谩cha, Ond艡ej; Kankaanp盲盲, Reeta; Kantorowicz, Jaroslaw; Kantorowicz-Reznichenko, Elena; Mintz, Keren Kaplan; Kaya, Ilker; Kaya, Ozgur; Khachatryan, Narine; Klas, Anna; Klein, Colin; Kl枚ckner, Christian A; Koppel, Lina; Kosachenko, Alexandra I; Kothe, Emily J; Krebs, Ruth; Krosch, Amy R; Krouwel, Andre P M; Kyrychenko, Yara; Lagomarsino, Maria; Lamm, Claus; Lange, Florian; Cunningham, Julia Lee; Lees, Jeffrey; Leung, Tak Yan; Levy, Neil; Lockwood, Patricia L; Longoni, Chiara; Ortega, Alberto L贸pez; Loschelder, David D; Lu, Jackson G; Luo, Yu; Luomba, Joseph; Lutz, Annika E; Majer, Johann M; Markowitz, Ezra; Marsh, Abigail A; Mascarenhas, Karen Louise; Mbilingi, Bwambale; Mbungu, Winfred; McHugh, Cillian; Meijers, Marijn H C; Mercier, Hugo; Mhagama, Fenant Laurent; Michalakis, Katerina; Mikus, Nace; Milliron, Sarah; Mitkidis, Panagiotis; Monge-Rodr铆guez, Fredy S; Mora, Youri L; Moreau, David; Motoki, Kosuke; Moyano, Manuel; Mus, Mathilde; Navajas, Joaquin; Nguyen, Tam Luong; Nguyen, Dung Minh; Nguyen, Trieu; Niemi, Laura; Nijssen, Sari R R; Nilsonne, Gustav; Nitschke, Jonas P; Nockur, Laila; Okura, Ritah; 脰ner, Sezin; 脰zdo臒ru, Asil Ali; Palumbo, Helena; Panagopoulos, Costas; Panasiti, Maria Serena; P盲rnamets, Philip; Paruzel-Czachura, Mariola; Pavlov, Yuri G; Pay谩n-G贸mez, C茅sar; Pearson, Adam R</t>
+  </si>
+  <si>
+    <t>Addressing climate change with behavioral science: A global intervention tournament in 63 countries</t>
+  </si>
+  <si>
+    <t>Wang, Ke; Goldenberg, Amit; Dorison, Charles A.; Miller, Jeremy K.; Uusberg, Andero; Lerner, Jennifer S.; Gross, James J.; Agesin, Bamikole Bamikole; Bernardo, M谩rcia; Campos, Olatz; Eudave, Luis; Grzech, Karolina; Ozery, Daphna Hausman; Jackson, Emily A.; Garcia, Elkin Oswaldo Luis; Drexler, Shira Meir; Jurkovi膰, Anita Peni膰; Rana, Kafeel; Wilson, John Paul; Antoniadi, Maria; Desai, Kermeka; Gialitaki, Zoi; Kushnir, Elizaveta; Nadif, Khaoula; Bravo, Olalla Ni帽o; Nauman, Rafia; Oosterlinck, Marlies; Pantazi, Myrto; Pilecka, Natalia; Szabelska, Anna; van Steenkiste, I. M. M.; Filip, Katarzyna; Bozdoc, Andreea Ioana; Marcu, Gabriela Mariana; Agadullina, Elena; Adamkovi膷, Mat煤拧; Roczniewska, Marta; Reyna, Cecilia; Kassianos, Angelos P.; Westerlund, Minja; Ahlgren, Lina; P枚ntinen, Sara; Adetula, Gabriel Agboola; Dursun, Pinar; Arinze, Azuka Ikechukwu; Arinze, Nwadiogo Chisom; Ogbonnaya, Chisom Esther; Ndukaihe, Izuchukwu L. G.; Dalgar, Ilker; Akkas, Handan; Macapagal, Paulo Manuel; Lewis, Savannah; Metin-Orta, Irem; Foroni, Francesco; Willis, Megan; Santos, Anabela Caetano; Mokady, Aviv; Reggev, Niv; Kurfali, Merve A.; Vasilev, Martin R.; Nock, Nora L.; Parzuchowski, Michal; Espinoza Barr铆a, Mauricio F.; Vranka, Marek; Kohlov谩, Mark茅ta Braun; Ropovik, Ivan; Harutyunyan, Mikayel; Wang, Chunhui; Yao, Elvin; Becker, Maja; Manunta, Efisio; Kaminski, Gwenael; Boudesseu, Jordane; Marko, Dafne; Evans, Kortnee; Lewis, David M. G.; Findor, Andrej; Landry, Anais Thibault; Aruta, John Jamir Benzon; Ortiz, Manuel S.; Vally, Zahir; Pronizius, Ekaterina; Voracek, Martin; Lamm, Claus; Grinberg, Maurice; Li, Ranran; Valentova, Jaroslava Varella; Mioni, Giovanna; Cellini, Nicola; Chen, Sau-Chin; Zickfeld, Janis; Moon, Karis; Azab, Habiba; Levy, Neil; Karababa, Alper; Beaudry, Jennifer L.; Boucher, Leanne; Collins, W. Matthew; Todsen, Anna Louise; van Schie, Kevin; Vintr, J谩chym; Bavolar, Jozef; Kaliska, Lada; Kri啪ani膰, Valerija; Samojlenko, Lara; Pourafshari, Razieh; Geiger, Sandra J.; Beitner, Julia; Warmelink, Lara; Ross, Robert M.; Stephen, Ian D.; Hostler, Thomas J.; Azouaghe, Soufian; McCarthy, Randy; Szala, Anna; Grano, Caterina; Solorzano, Claudio Singh; Anjum, Gulnaz; Jimenez-Leal, William; Bradford, Maria; P茅rez, Laura Calder贸n; Cruz V谩squez, Julio E.; Galindo-Caballero, Oscar J.; Vargas-Nieto, Juan Camilo; K谩cha, Ond艡ej; Arvanitis, Alexios; Xiao, Qinyu; C谩rcamo, Rodrigo; Zorjan, Sa拧a; Tajchman, Zuzanna; Vilares, Iris; Pavlacic, Jeffrey M.; Kunst, Jonas R.; Tamnes, Christian K.; von Bastian, Claudia C.; Atari, Mohammad; Sharifian, MohammadHasan; Hricova, Monika; Ka膷m谩r, Pavol; Schr枚tter, Jana; Rahal, Rima-Maria; Cohen, Noga; FatahModares, Saeideh; Zrimsek, Miha; Zakharov, Ilya; Koehn, Monica A.; Esteban-Serna, Celia; Calin-Jageman, Robert J.; Krafnick, Anthony J.; 艩trukelj, Eva; Isager, Peder Mortvedt; Urban, Jan; Silva, Jaime R.; Marton膷ik, Marcel; O膷ovaj, Sanja Bati膰; 艩akan, Du拧ana; Kuzminska, Anna O.; Djordjevic, Jasna Milosevic; Almeida, In锚s A. T.; Ferreira, Ana; Lazarevic, Ljiljana B.; Manley, Harry; Ricaurte, Danilo Zambrano; Monteiro, Renan P.; Etabari, Zahra; Musser, Erica; Dunleavy, Daniel; Chou, Weilun; Godbersen, Hendrik; Ruiz-Fern谩ndez, Susana; Reeck, Crystal; Batres, Carlota; Kirgizova, Komila; Muminov, Abdumalik; Azevedo, Flavio; Alvarez, Daniela Serrato; Butt, Muhammad Mussaffa; Lee, Jeong Min; Chen, Zhang; Verbruggen, Frederick; Ziano, Ignazio; T眉mer, Murat; Charyate, Abdelilah C. A.; Dubrov, Dmitrii; Tejada Rivera, Mar铆a del Carmen M. C.; Aberson, Christopher; P谩lfi, Bence; Maldonado, M贸nica Alarc贸n; Hubena, Barbora; Sacakli, Asli; Ceary, Chris D.; Richard, Karley L.; Singer, Gage; Perillo, Jennifer T.; Ballantyne, Tonia; Cyrus-Lai, Wilson; Fedotov, Maksim; Du, Hongfei; Wielgus, Magdalena; Pit, Ilse L.; Hru拧ka, Matej; Sousa, Daniela; Aczel, Balazs; Hajdu, Nandor; Szaszi, Barnabas; Adamus, Sylwia; Barzykowski, Krystian; Micheli, Leticia; Schmidt, Nadya-Daniela; Zsido, Andras N.; Paruzel-Czachura, Mariola; Muda, Rafa艂; Bialek, Michal; Kowal, Marta; Sorokowska, Agnieszka; Misiak, Michal; Mola, D茅bora; Ortiz, Mar铆a Victoria; Correa, Pablo Sebasti谩n; Belaus, Anabel; Muchembled, Fany; Ribeiro, Rafael R.; Arriaga, Patricia; Oliveira, Raquel; Vaughn, Leigh Ann; Szwed, Paulina; Kossowska, Ma艂gorzata; Czarnek, Gabriela; Kieli艅ska, Julita; Antazo, Benedict; Betlehem, Ruben; Stieger, Stefan; Nilsonne, Gustav; Simonovic, Nicolle; Taber, Jennifer; Gourdon-Kanhukamwe, Am茅lie; Domurat, Artur; Ihaya, Keiko; Yamada, Yuki; Urooj, Anum; Gill, Tripat; 膶adek, Martin; Bylinina, Lisa; Messerschmidt, Johanna; Kurfal谋, Murathan; Adetula, Adeyemi; Baklanova, Ekaterina; Albayrak-Aydemir, Nihan; Kappes, Heather B.; Gjoneska, Biljana; House, Thea; Jones, Marc V.; Berkessel, Jana B.; Chopik, William J.; 脟oksan, Sami; Seehuus, Martin; Khaoudi, Ahmed; Bokkour, Ahmed; El Arabi, Kanza Ait; Djamai, Ikhlas; Iyer, Aishwarya; Parashar, Neha; Adiguzel, Arca; Kocalar, Halil Emre; Bundt, Carsten; Norton, James O.; Papadatou-Pastou, Marietta; De la Rosa-Gomez, Anabel; Ankushev, Vladislav; Bogatyreva, Natalia; Grigoryev, Dmitry; Ivanov, Aleksandr; Prusova, Irina; Romanova, Marina; Sarieva, Irena; Terskova, Maria; Hristova, Evgeniya; Kadreva, Veselina Hristova; Janak, Allison; Schei, Vidar; Sverdrup, Therese E.; Askelund, Adrian Dahl; Pineda, Lina Maria Sanabria; Krupi膰, Dajana; Levitan, Carmel A.; Johannes, Niklas; Ouherrou, Nihal; Say, Nicolas; Sinkolova, Sladjana; Janji膰, Kristina; Stojanovska, Marija; Stojanovska, Dragana; Khosla, Meetu; Thomas, Andrew G.; Kung, Franki Y. H.; Bijlstra, Gijsbert; Mosannenzadeh, Farnaz; Balci, Busra Bahar; Reips, Ulf-Dietrich; Baskin, Ernest; Ishkhanyan, Byurakn; Czamanski-Cohen, Johanna; Dixson, Barnaby James Wyld; Moreau, David; Sutherland, Clare A. M.; Chuan-Peng, Hu; Noone, Chris; Flowe, Heather; Anne, Michele; Janssen, Steve M. J.; Topor, Marta; Majeed, Nadyanna M.; Kunisato, Yoshihiko; Yu, Karen; Daches, Shimrit; Hartanto, Andree; Vdovic, Milica; Anton-Boicuk, Lisa; Forbes, Paul A. G.; Kamburidis, Julia; Marinova, Evelina; Nedelcheva-Datsova, Mina; Rachev, Nikolay R.; Stoyanova, Alina; Schmidt, Kathleen; Suchow, Jordan W.; Koptjevskaja-Tamm, Maria; Jerns盲ther, Teodor; Olofsson, Jonas K.; Bialobrzeska, Olga; Marszalek, Magdalena; Tatachari, Srinivasan; Afhami, Reza; Law, Wilbert; Antfolk, Jan; 沤uro, Barbara; Van Doren, Natalia; Soto, Jose A.; Searston, Rachel; Miranda, Jacob; Damnjanovi膰, Kaja; Yeung, Siu Kit; Krupi膰, Dino; Hoyer, Karlijn; Jaeger, Bastian; Ren, Dongning; Pfuhl, Gerit; Klevjer, Kristoffer; Corral-Fr铆as, Nadia S.; Frias-Armenta, Martha; Lucas, Marc Y.; Torres, Adriana Olaya; Toro, M贸nica; Delgado, Lady Grey Javela; Vega, Diego; Solas, Sara 脕lvarez; Vilar, Roosevelt; Massoni, S茅bastien; Frizzo, Thomas; Bran, Alexandre; Vaidis, David C.; Vieira, Luc; Paris, Bastien; Capizzi, Mariagrazia; Coelho, Gabriel Lins de Holanda; Greenburgh, Anna; Whitt, Cassie M.; Tullett, Alexa M.; Du, Xinkai; Volz, Leonhard; Bosma, Minke Jasmijn; Karaarslan, Cemre; Sar谋o臒uz, Eyl眉l; Allred, Tara Bulut; Korbmacher, Max; Colloff, Melissa F.; Lima, Tiago J. S.; Ribeiro, Matheus Fernando Felix; Verharen, Jeroen P. H.; Karekla, Maria; Karashiali, Christiana; Sunami, Naoyuki; Jaremka, Lisa M.; Storage, Daniel; Habib, Sumaiya; Studzinska, Anna; Hanel, Paul H. P.; Holford, Dawn Liu; Sirota, Miroslav; Wolfe, Kelly; Chiu, Faith; Theodoropoulou, Andriana; Ahn, El Rim; Lin, Yijun; Westgate, Erin C.; Brohmer, Hilmar; Hofer, Gabriela; Dujols, Olivier; Vezirian, Kevin; Feldman, Gilad; Travaglino, Giovanni A.; Ahmed, Afroja; Li, Manyu; Bosch, Jasmijn; Torunsky, Nathan; Bai, Hui; Manavalan, Mathi; Song, Xin; Walczak, Radoslaw B.; Zdybek, Przemys艂aw; Friedemann, Maja; Rosa, Anna Dalla; Kozma, Luca; Alves, Sara G.; Lins, Samuel; Pinto, Isabel R.; Correia, Rita C.; Babin膷谩k, Peter; Banik, Gabriel; Rojas-Berscia, Luis Miguel; Varella, Marco A. C.; Uttley, Jim; Beshears, Julie E.; Thommesen, Katrine Krabbe; Behzadnia, Behzad; Geniole, Shawn N.; Silan, Miguel A.; Maturan, Princess Lovella G.; Vilsmeier, Johannes K.; Tran, Ulrich S.; Izquierdo, Sara Morales; Mensink, Michael C.; Sorokowski, Piotr; Groyecka-Bernard, Agata; Radtke, Theda; Adoric, Vera Cubela; Carpentier, Joelle; 脰zdo臒ru, Asil Ali; Joy-Gaba, Jennifer A.; Hedgebeth, Mattie V.; Ishii, Tatsunori; Wichman, Aaron L.; R枚er, Jan Philipp; Ostermann, Thomas; Davis, William E.; Suter, Lilian; Papachristopoulos, Konstantinos; Zabel, Chelsea; Onie, Sandersan; Ebersole, Charles R.; Chartier, Christopher R.; Mallik, Peter R.; Urry, Heather L.; Buchanan, Erin M.; Coles, Nicholas A.; Primbs, Maximilian A.; Basnight-Brown, Dana M.; IJzerman, Hans; Forscher, Patrick S.; Moshontz, Hannah</t>
+  </si>
+  <si>
+    <t>A multi-country test of brief reappraisal interventions on emotions during the COVID-19 pandemic</t>
+  </si>
+  <si>
+    <t>Reappraisal, Emotions, COVID-19, Multi-country, Interventions</t>
+  </si>
+  <si>
+    <t>Wasiel, Arkadiusz; G贸rski, Maciej R.; Bond, Michael Harris; Yeung, Victoria Wai Lan; Akaliyski, Plamen; Akello, Grace; Park, Joonha; Joshanloo, Mohsen; Sokolov, Boris; Hussain, M. Azhar; Li, Liman Man Wai; Olechowski, Mateusz; Vignoles, Vivian L.; Guemaz, Farida; Boussena, Mahmoud; Rabby, Md. Reza-A; Okvitawanli, Ayu; My艣li艅ska-Szarek, Katarzyna; Haas, Brian W.; S谩nchez-Rodr铆guez, 脕ngel; Vlasenko, Olha; Lun, Vivian Miu-Chi; Aminnuddin, Nur Amali; I艧谋k, 陌dil; Barry, Oumar; F眉l枚p, M谩rta; Igbokwe, David; Adamovic, Mladen; Gar冒arsd贸ttir, Ragna Benedikta; Soboleva, Natalia; Teyssier, Julien; Gl眉ckstad, Fumiko Kano; Samekin, Adil; Akotia, Charity; Al-Zoubi, Marwan; Andrade, Laura; Ani膰, Petra; Bakyono-Nabaloum, Rasmata; Baltin, Arno; Costin, Vlad; Denoux, Patrick; Espinosa, Alejandra Dom铆nguez; Espinosa, Agustin; Gamsakhurdia, Vladimer; Garvanova, Magdalena; Gavreliuc, Alin; Gjoneska, Biljana; Igou, Eric Raymond; Iqbal, Naved; Iter, Nuha; Kascakova, Natalia; Kazimzade, Elmina; Kluzowicz, Maria; Kocimska-Bortnowska, Agata; Kronberger, Nicole; Lauri, Mary Anne; Lee, Hannah; Malyonova, Arina; Maricchiolo, Fridanna; Mohammed, Linda; Mokadem, Fatma; Mosanya, Magdalena; Mosca, Oriana; Murdock, Elke; Nader, Martin; Nowak, Karolina; Ochoa, Danielle; Pavlovi膰, Zoran; 艩olcov谩, Iva Pol谩膷kov谩; Purc, Ewelina; Rizwan, Muhammad; Rocha, Ana Maria; Selim, Heyla; Sobhie, Rosita; Streng, Moritz; Sun, Chien-Ru; T酶nnessen, Morten; Torres, Claudio; Tr脿, Ki峄乽 Th峄?Thanh; Turja膷anin, Vladimir; van Tilburg, Wijnand; Vauclair, Christin-Melanie; Vergara-Morales, Jorge; Xing, Cai; Yakhlef, Belkacem; Yang, Jae-Won; Yau, Eric Kenson; Yeung, June Chun; Zelenski, John; Krys, Kuba</t>
+  </si>
+  <si>
+    <t>22Examining the connection between position-based power and social status across 70 cultures</t>
+  </si>
+  <si>
+    <t>Power, Social Status, Culture, Self-Orientation, Other-Orientation</t>
+  </si>
+  <si>
+    <t>Yik, Michelle; Mues, Chiel; Sze, Irene N. L.; Kuppens, Peter; Tuerlinckx, Francis; De Roover, Kim; Kwok, Felity H. C.; Schwartz, Shalom H.; Abu-Hilal, Maher; Adebayo, Damilola Fisayo; Aguilar, Pilar; Al-Bahrani, Muna; Anderson, Marc H.; Andrade, Laura; Bratko, Denis; Bushina, Ekaterina; Choi, Jeong Won; Cieciuch, Jan; Dru, Vincent; Evers, Uwana; Fischer, Ronald; Florez, Ivonne Andrea; Gar冒arsd贸ttir, Ragna B.; Gari, Aikaterini; Graf, Sylvie; Halama, Peter; Halberstadt, Jamin; Halim, Magdalena S.; Heilman, Renata M.; H艡eb铆膷kov谩, Martina; Karl, Johannes Alfons; Kne啪evi膰, Goran; Koh煤t, Michal; Kolnes, Martin; Lazarevi膰, Ljiljana B.; Lebedeva, Nadezhda; Lee, Julie; Lee, Young-Ho; Liu, Chunquan; Mannerstr枚m, Rasmus; Maru拧i膰, Iris; Nansubuga, Florence; Ojedokun, Oluyinka; Park, Joonha; Platt, Tracey; Proyer, Ren茅 T.; Realo, Anu; Rolland, Jean-Pierre; Ruch, Willibald; Ruiz, Desiree; Sortheix, Florencia M.; Stahlmann, Alexander Georg; Stojanov, Ana; Strus, W艂odzimierz; Tamir, Maya; Torres, Cl谩udio; Trujillo, Angela; Truong, Thi Khanh Ha; Utsugi, Akira; Vecchione, Michele; Wang, Lei; Russell, James A.</t>
+  </si>
+  <si>
+    <t>22On the relationship between valence and arousal in samples across the globe</t>
+  </si>
+  <si>
+    <t>valence, arousal, subjective experience, structure of affect, culture</t>
+  </si>
+  <si>
+    <t>Zickfeld, Janis H.; van de Ven, Niels; Pich, Olivia; Schubert, Thomas W.; Berkessel, Jana B.; Pizarro, Jos茅 J.; Bhushan, Braj; Mateo, Nino Jose; Barbosa, Sergio; Sharman, Leah; K枚k枚nyei, Gy枚ngyi; Schrover, Elke; Kardum, Igor; Aruta, John Jamir Benzon; Lazarevic, Ljiljana B.; Escobar, Mar铆a Josefina; Stadel, Marie; Arriaga, Patr铆cia; Dodaj, Arta; Shankland, Rebecca; Majeed, Nadyanna M.; Li, Yansong; Lekkou, Eleimonitria; Hartanto, Andree; 脰zdo臒ru, Asil A.; Vaughn, Leigh Ann; del Carmen Espinoza, Maria; Caballero, Amparo; Kolen, Anouk; Karsten, Julie; Manley, Harry; Maeura, Nao; E艧kisu, Mustafa; Shani, Yaniv; Chittham, Phakkanun; Ferreira, Diogo; Bavolar, Jozef; Konova, Irina; Sato, Wataru; Morvinski, Coby; Carrera, Pilar; Villar, Sergio; Ibanez, Agustin; Hareli, Shlomo; Garcia, Adolfo M.; Kremer, Inbal; G枚tz, Friedrich M.; Schwerdtfeger, Andreas; Estrada-Mejia, Catalina; Nakayama, Masataka; Ng, Wee Qin; Sesar, Kristina; Orjiakor, Charles T.; Dumont, Kitty; Allred, Tara Bulut; Gra膷anin, Asmir; Rentfrow, Peter J.; Sch枚nefeld, Victoria; Vally, Zahir; Barzykowski, Krystian; Peltola, Henna-Riikka; Tcherkassof, Anna; Haque, Shamsul; 艢mieja, Magdalena; Su-May, Terri Tan; IJzerman, Hans; Vatakis, Argiro; Ong, Chew Wei; Choi, Eunsoo; Schorch, Sebastian L.; P谩ez, Dar铆o; Malik, Sadia; Ka膷m谩r, Pavol; Bobowik, Magdalena; Jose, Paul; Vuoskoski, Jonna K.; Basabe, Nekane; Do臒an, U臒ur; Ebert, Tobias; Uchida, Yukiko; Zheng, Michelle Xue; Mefoh, Philip; 艩ebe艌a, Ren茅; Stanke, Franziska A.; Ballada, Christine Joy; Blaut, Agata; Wu, Yang; Daniels, Judith K.; Kocsel, Nat谩lia; Burak, Elif Gizem Demirag; Balt, Nina F.; Vanman, Eric; Stewart, Suzanne L. K.; Verschuere, Bruno; Sikka, Pilleriin; Boudesseul, Jordane; Martins, Diogo; Nussinson, Ravit; Ito, Kenichi; Mentser, Sari; 脟olak, Tu臒ba Seda; Martinez-Zelaya, Gonzalo; Vingerhoets, Ad</t>
+  </si>
+  <si>
+    <t>Tears evoke the intention to offer social support: A systematic investigation of the interpersonal effects of emotional crying across 41 countries</t>
+  </si>
+  <si>
+    <t>Anger and disgust shape judgments of social sanctions across cultures, especially in high individual autonomy societies</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>COVID-19, social attitudes, identity, moral beliefs, compliance behaviours</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>thinking, individual differences, cultural differences, replication</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Moral judgement, personal force effect, replication, Cultural universality, Trolley dilemma</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Semantic Priming Effect, Cross-linguistic variability, Response latency, Semantic Similarity, Registered Report</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Psychological Science Accelerator's COVID-19 rapid-response dataset</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gaze Following, Bilingual Infants, Monolingual Infants, multi-laboratory study, Developmental Trajectory</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>cross-lingual research, language comprehension, mental rotation, mental simulation</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Facial feedback hypothesis, Facial mimicry task, Voluntary facial action task, Pen-in-mouth task, Emotional experience</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Trust in scientists, Science-related populism, Social dominance orientation, Political orientation, Role of scientists in society</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Experimental Philosophy, Reproducibility, Replication, Effect Size, representative sample</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>climate change, behavioral interventions, global study, beliefs, policy support</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>scientific consensus, climate change, misperceptions, climate change beliefs, worry</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>remote web-based eye-tracking, WebGazer, toddlers, anticipatory looking, validation</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Modernization, collectivism, gender equality, love experiences, Triangular Theory of Love</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Group meta-perceptions, Political polarization, Replication, Intergroup relations, Cross-cultural generalizability</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>temporal discounting, globalizability, intertemporal choice, economic inequality, financial circumstances</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>brain-age, Latin America and Caribbean countries (LAC), functional magnetic resonance imaging (fMRI), electroencephalography (EEG), Alzheimer disease</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>valence–dominance model, valence, dominance, faces, social judgements</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Conspiracy mentality, Political orientation, Cross-national, Quadratic relationship, Political control deprivation</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data from the Human Penguin Project, a cross-national dataset testing social thermoregulation principles</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>social thermoregulation, social networks, geographical, climate, cross-national dataset</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dataset, Loss-Gain Framing, Cognitive Reappraisal, Self-Determination Theory, COVID-19</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Brain clocks capture diversity and disparities in aging and dementia across geographically diverse populations</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Elb忙k, Christian T.; Mitkidis, Panagiotis; Aar酶e, Lene; Otterbring, Tobias</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Emotional crying, Emotional tears, Attachment, Cross-cultural, Social support</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sustainable, Education, Environment, Students,  Global Survey</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>Data from an International Multi-Centre Study of Statistics and Mathematics Anxieties and Related Variables in University Students (the SMARVUS Dataset)</t>
-  </si>
-  <si>
-    <t>The ManyBabies Consortium</t>
-  </si>
-  <si>
-    <t>Quantifying Sources of Variability in Infancy Research Using the Infant-Directed-Speech Preference</t>
-  </si>
-  <si>
-    <t>language acquisition, speech perception, infant-directed speech, reproducibility, experimental methods, open data, open materials, preregistered</t>
-  </si>
-  <si>
-    <t>Tybur, Joshua M.; Inbar, Yoel; Aar酶e, Lene; Barclay, Pat; Barlow, Fiona Kate; de Barra, M铆che谩l; Becker, D. Vaughn; Borovoi, Leah; Choi, Incheol; Choi, Jong An; Consedine, Nathan S.; Conway, Alan; Conway, Jane Rebecca; Conway, Paul; Adoric, Vera Cubela; Demirci, Dilara Ekin; Fern谩ndez, Ana Mar铆a; Ferreira, Diogo Conque Seco; Ishii, Keiko; Jak拧i膰, Ivana; Ji, Tingting; van Leeuwen, Florian; Lewis, David M. G.; Li, Norman P.; McIntyre, Jason C.; Mukherjee, Sumitava; Park, Justin H.; Pawlowski, Boguslaw; Petersen, Michael Bang; Pizarro, David; Prodromitis, Gerasimos; Prokop, Pavol; Rantala, Markus J.; Reynolds, Lisa M.; Sandin, Bonifacio; Sevi, Bari艧; De Smet, Delphine; Srinivasan, Narayanan; Tewari, Shruti; Wilson, Cameron; Yong, Jose C.; 沤e啪elj, Iris</t>
-  </si>
-  <si>
-    <t>Parasite stress and pathogen avoidance relate to distinct dimensions of political ideology across 30 nations</t>
-  </si>
-  <si>
-    <t>political ideology, pathogens, disgust, culture, evolutionary psychology</t>
-  </si>
-  <si>
-    <t>Van Bavel, Jay J.; Cichocka, Aleksandra; Capraro, Valerio; Sj氓stad, Hallgeir; Nezlek, John B.; Pavlovi膰, Tomislav; Alfano, Mark; Gelfand, Michele J.; Azevedo, Flavio; Birtel, Mich猫le D.; Cislak, Aleksandra; Lockwood, Patricia L.; Ross, Robert Malcolm; Abts, Koen; Agadullina, Elena; Aruta, John Jamir Benzon; Besharati, Sahba Nomvula; Bor, Alexander; Choma, Becky L.; Crabtree, Charles David; Cunningham, William A.; De, Koustav; Ejaz, Waqas; Elbaek, Christian T.; Findor, Andrej; Flichtentrei, Daniel; Franc, Renata; Gjoneska, Biljana; Gruber, June; Gualda, Estrella; Horiuchi, Yusaku; Huynh, Toan Luu Duc; Ibanez, Agustin; Imran, Mostak Ahamed; Israelashvili, Jacob; Jasko, Katarzyna; Kantorowicz, Jaroslaw; Kantorowicz-Reznichenko, Elena; Krouwel, Andr茅; Laakasuo, Michael; Lamm, Claus; Leygue, Caroline; Lin, Ming-Jen; Mansoor, Mohammad Sabbir; Marie, Antoine; Mayiwar, Lewend; Mazepus, Honorata; McHugh, Cillian; Minda, John Paul; Mitkidis, Panagiotis; Olsson, Andreas; Otterbring, Tobias; Packer, Dominic J.; Perry, Anat; Petersen, Michael Bang; Puthillam, Arathy; Ria帽o-Moreno, Juli谩n C.; Rothmund, Tobias; Santamar铆a-Garc铆a, Hernando; Schmid, Petra C.; Stoyanov, Drozdstoy; Tewari, Shruti; Todosijevi膰, Bojan; Tsakiris, Manos; Tung, Hans H.; Umbre葯, Radu G.; Vanags, Edmunds; Vlasceanu, Madalina; Vonasch, Andrew; Yucel, Meltem; Zhang, Yucheng; Abad, Mohcine; Adler, Eli; Akrawi, Narin; Mdarhri, Hamza Alaoui; Amara, Hanane; Amodio, David M.; Antazo, Benedict G.; Apps, Matthew; Ay, F. Ceren; Ba, Mouhamadou Hady; Barbosa, Sergio; Bastian, Brock; Berg, Anton; Bernal-Z谩rate, Maria P.; Bernstein, Michael; Bia艂ek, Micha艂; Bilancini, Ennio; Bogatyreva, Natalia; Boncinelli, Leonardo; Booth, Jonathan E.; Borau, Sylvie; Buchel, Ondrej; Cameron, C. Daryl; Carvalho, Chrissie F.; Celadin, Tatiana; Cerami, Chiara; Chalise, Hom Nath; Cheng, Xiaojun; Cian, Luca; Cockcroft, Kate; Conway, Jane; C贸rdoba-Delgado, Mateo Andres; Crespi, Chiara; Crouzevialle, Marie; Cutler, Jo; Cyprya艅ska, Marzena; Dabrowska, Justyna; Daniels, Michael A.; Davis, Victoria H.; Dayley, Pamala N.; Delouvee, Sylvain; Denkovski, Ognjan; Dezecache, Guillaume; Dhaliwal, Nathan A.; Diato, Alelie B.; Di Paolo, Roberto; Drosinou, Marianna; Dulleck, Uwe; Ekmanis, J膩nis; Ertan, Arhan S.; Etienne, Tom W.; Farhana, Hapsa Hossain; Farkhari, Fahima; Farmer, Harry; Fenwick, Ali; Fidanovski, Kristijan; Flew, Terry; Fraser, Shona; Frempong, Raymond Boadi; Fugelsang, Jonathan A.; Gale, Jessica; Garcia-Navarro, E. Bego帽a; Garladinne, Prasad; Ghajjou, Oussama; Gkinopoulos, Theofilos; Gray, Kurt; Griffin, Siobh谩n M.; Gronfeldt, Bjarki; G眉mren, Mert; Gurung, Ranju Lama; Halperin, Eran; Harris, Elizabeth; Herzon, Volo; Hru拧ka, Matej; Huang, Guanxiong; Hudecek, Matthias F. C.; Isler, Ozan; Jangard, Simon; J酶rgensen, Frederik J.; Kachanoff, Frank; Kahn, John; Dangol, Apsara Katuwal; Keudel, Oleksandra; Koppel, Lina; Koverola, Mika; Kubin, Emily; Kunnari, Anton; Kutiyski, Yordan; Laguna, Oscar; Leota, Josh; Lermer, Eva; Levy, Jonathan; Levy, Neil; Li, Chunyun; Long, Elizabeth U.; Longoni, Chiara; Magli膰, Marina; McCashin, Darragh; Metcalf, Alexander L.; Miklou拧i膰, Igor; El Mimouni, Soulaimane; Miura, Asako; Molina-Paredes, Juliana; Monroy-Fonseca, C茅sar; Morales-Marente, Elena; Moreau, David; Muda, Rafa艂; Myer, Annalisa; Nash, Kyle; Nesh-Nash, Tarik; Nitschke, Jonas P.; Nurse, Matthew S.; Ohtsubo, Yohsuke; Oldemburgo de Mello, Victoria; O鈥橫adagain, Cathal; Onderco, Michal; Palacios-Galvez, M. Soledad; Palom盲ki, Jussi; Pan, Yafeng; Papp, Zs贸fia; P盲rnamets, Philip; Paruzel-Czachura, Mariola; Pavlovi膰, Zoran; Pay谩n-G贸mez, C茅sar; Perander, Silva; Pitman, Michael Mark; Prasad, Rajib; Pyrkosz-Pacyna, Joanna; Rathje, Steve; Raza, Ali; R锚go, Gabriel G.; Rhee, Kasey; Robertson, Claire E.; Rodr铆guez-Pascual, Iv谩n; Saikkonen, Teemu; Salvador-Ginez, Octavio; Sampaio, Waldir M.; Santi, Gaia C.; Santiago-Tovar, Natalia; Savage, David; Scheffer, Julian A.; Sch枚negger, Philipp; Schultner, David T.; Schutte, Enid M.; Scott, Andy; Sharma, Madhavi; Sharma, Pujan; Skali, Ahmed; Stadelmann, David; Stafford, Clara Alexandra; Stanojevi膰, Dragan; Stefaniak, Anna; Sternisko, Anni; Stoica, Agustin; Stoyanova, Kristina K.; Strickland, Brent; Sundvall, Jukka; Thomas, Jeffrey P.; Tingh枚g, Gustav; Torgler, Benno; Traast, Iris J.; Tucciarelli, Raffaele; Tyrala, Michael; Ungson, Nick D.; Uysal, Mete S.; Van Lange, Paul A. M.; van Prooijen, Jan-Willem; van Rooy, Dirk; V盲stfj盲ll, Daniel; Verkoeijen, Peter; Vieira, Joana B.; von Sikorski, Christian; Walker, Alexander Cameron; Watermeyer, Jennifer; Wetter, Erik; Whillans, Ashley; Willardt, Robin; Wohl, Michael J. A.; W贸jcik, Adrian Dominik; Wu, Kaidi; Yamada, Yuki; Yilmaz, Onurcan; Yogeeswaran, Kumar; Ziemer, Carolin-Theresa; Zwaan, Rolf A.; Boggio, Paulo S.</t>
-  </si>
-  <si>
-    <t>National identity predicts public health support during a global pandemic</t>
-  </si>
-  <si>
-    <t>national identity, public health support, COVID-19 pandemic, behavioral science, social identity</t>
-  </si>
-  <si>
-    <t>Ve膰kalov, Bojana; Geiger, Sandra J.; Barto拧, Franti拧ek; White, Mathew P.; Rutjens, Bastiaan T.; van Harreveld, Frenk; Stablum, Federica; Ak谋n, Berkan; Aldoh, Alaa; Bai, Jinhao; Berglund, Frida; Bratina Zimic, Ale拧a; Broyles, Margaret; Catania, Andrea; Chen, Airu; Chorz臋pa, Magdalena; Farahat, Eman; G枚tz, Jakob; Hoter-Ishay, Bat; Jordan, Gesine; Joustra, Siri; Klingebiel, Jonas; Krajnc, 沤iva; Krug, Antonia; Andersen, Thomas Lind; L枚loff, Johanna; Natarajan, Divya; Newman-Oktan, Sasha; Niehoff, Elena; Paerels, Celeste; Papirmeister, Rachel; Peregrina, Steven; Pohl, Felicia; Rems枚, Amanda; Roh, Abigail; Rusyidi, Binahayati; Schmidt, Justus; Shavgulidze, Mariam; Vellinho Nardin, Valentina; Wang, Ruixiang; Warner, Kelly; Wattier, Miranda; Wong, Chloe Y.; Younssi, Mariem; Ruggeri, Kai; van der Linden, Sander</t>
-  </si>
-  <si>
-    <t>A 27-country test of communicating the scientific consensus on climate change</t>
-  </si>
-  <si>
-    <t>Vlasceanu, Madalina; Doell, Kimberly C; Bak-Coleman, Joseph B; Todorova, Boryana; Berkebile-Weinberg, Michael M; Grayson, Samantha J; Patel, Yash; Goldwert, Danielle; Pei, Yifei; Chakroff, Alek; Pronizius, Ekaterina; Constantino, Sara; Morais, Michael J; Schumann, Philipp; Rathje, Steve; Fang, Ke; Aglioti, Salvatore Maria; Alfano, Mark; Alvarado-Yepez, Andy J; Andersen, Ang茅lica; Anseel, Frederik; Apps, Matthew A J; Asadli, Chillar; Awuor, Fonda Jane; Azevedo, Flavio; Basaglia, Piero; B茅langer, Jocelyn J; Berger, Sebastian; Bertin, Paul; Bia艂ek, Micha艂; Bialobrzeska, Olga; Blaya-Burgo, Michelle; Bleize, Dani毛lle N M; B酶, Simen; Boecker, Lea; Boggio, Paulo S; Borau, Sylvie; Bos, Bj枚rn; Bouguettaya, Ayoub; Brauer, Markus; Brick, Cameron; Brik, Tymofii; Briker, Roman; Brosch, Tobias; Buchel, Ondrej; Buonauro, Daniel; Butalia, Radhika; Carvacho, H茅ctor; Chamberlain, Sarah A E; Chan, Hang-Yee; Chow, Dawn; Chung, Dongil; Cian, Luca; Cohen-Eick, Noa; Contreras-Huerta, Luis Sebastian; Contu, Davide; Cristea, Vladimir; Cutler, Jo; D'Ottone, Silvana; Keersmaecker, Jonas De; Delcourt, Sarah; Delouv茅e, Sylvain; Diel, Kathi; Douglas, Benjamin D; Drupp, Moritz A; Dubey, Shreya; Ekmanis, J膩nis; Elbaek, Christian T; Elsherif, Mahmoud; Engelhard, Iris M; Escher, Yannik A; Etienne, Tom W; Farage, Laura; Farias, Ana Rita; Feuerriegel, Stefan; Findor, Andrej; Freira, Lucia; Friese, Malte; Gains, Neil Philip; Gallyamova, Albina; Geiger, Sandra J; Genschow, Oliver; Gjoneska, Biljana; Gkinopoulos, Theofilos; Goldberg, Beth; Goldenberg, Amit; Gradidge, Sarah; Grassini, Simone; Gray, Kurt; Grelle, Sonja; Griffin, Siobh谩n M; Grigoryan, Lusine; Grigoryan, Ani; Grigoryev, Dmitry; Gruber, June; Guilaran, Johnrev; Hadar, Britt; Hahnel, Ulf J J; Halperin, Eran; Harvey, Annelie J; Haugestad, Christian A P; Herman, Aleksandra M; Hershfield, Hal E; Himichi, Toshiyuki; Hine, Donald W; Hofmann, Wilhelm; Howe, Lauren; Huaman-Chulluncuy, Enma T; Huang, Guanxiong; Ishii, Tatsunori; Ito, Ayahito; Jia, Fanli; Jost, John T; Jovanovi膰, Veljko; Jurgiel, Dominika; K谩cha, Ond艡ej; Kankaanp盲盲, Reeta; Kantorowicz, Jaroslaw; Kantorowicz-Reznichenko, Elena; Mintz, Keren Kaplan; Kaya, Ilker; Kaya, Ozgur; Khachatryan, Narine; Klas, Anna; Klein, Colin; Kl枚ckner, Christian A; Koppel, Lina; Kosachenko, Alexandra I; Kothe, Emily J; Krebs, Ruth; Krosch, Amy R; Krouwel, Andre P M; Kyrychenko, Yara; Lagomarsino, Maria; Lamm, Claus; Lange, Florian; Cunningham, Julia Lee; Lees, Jeffrey; Leung, Tak Yan; Levy, Neil; Lockwood, Patricia L; Longoni, Chiara; Ortega, Alberto L贸pez; Loschelder, David D; Lu, Jackson G; Luo, Yu; Luomba, Joseph; Lutz, Annika E; Majer, Johann M; Markowitz, Ezra; Marsh, Abigail A; Mascarenhas, Karen Louise; Mbilingi, Bwambale; Mbungu, Winfred; McHugh, Cillian; Meijers, Marijn H C; Mercier, Hugo; Mhagama, Fenant Laurent; Michalakis, Katerina; Mikus, Nace; Milliron, Sarah; Mitkidis, Panagiotis; Monge-Rodr铆guez, Fredy S; Mora, Youri L; Moreau, David; Motoki, Kosuke; Moyano, Manuel; Mus, Mathilde; Navajas, Joaquin; Nguyen, Tam Luong; Nguyen, Dung Minh; Nguyen, Trieu; Niemi, Laura; Nijssen, Sari R R; Nilsonne, Gustav; Nitschke, Jonas P; Nockur, Laila; Okura, Ritah; 脰ner, Sezin; 脰zdo臒ru, Asil Ali; Palumbo, Helena; Panagopoulos, Costas; Panasiti, Maria Serena; P盲rnamets, Philip; Paruzel-Czachura, Mariola; Pavlov, Yuri G; Pay谩n-G贸mez, C茅sar; Pearson, Adam R</t>
-  </si>
-  <si>
-    <t>Addressing climate change with behavioral science: A global intervention tournament in 63 countries</t>
-  </si>
-  <si>
-    <t>Wang, Ke; Goldenberg, Amit; Dorison, Charles A.; Miller, Jeremy K.; Uusberg, Andero; Lerner, Jennifer S.; Gross, James J.; Agesin, Bamikole Bamikole; Bernardo, M谩rcia; Campos, Olatz; Eudave, Luis; Grzech, Karolina; Ozery, Daphna Hausman; Jackson, Emily A.; Garcia, Elkin Oswaldo Luis; Drexler, Shira Meir; Jurkovi膰, Anita Peni膰; Rana, Kafeel; Wilson, John Paul; Antoniadi, Maria; Desai, Kermeka; Gialitaki, Zoi; Kushnir, Elizaveta; Nadif, Khaoula; Bravo, Olalla Ni帽o; Nauman, Rafia; Oosterlinck, Marlies; Pantazi, Myrto; Pilecka, Natalia; Szabelska, Anna; van Steenkiste, I. M. M.; Filip, Katarzyna; Bozdoc, Andreea Ioana; Marcu, Gabriela Mariana; Agadullina, Elena; Adamkovi膷, Mat煤拧; Roczniewska, Marta; Reyna, Cecilia; Kassianos, Angelos P.; Westerlund, Minja; Ahlgren, Lina; P枚ntinen, Sara; Adetula, Gabriel Agboola; Dursun, Pinar; Arinze, Azuka Ikechukwu; Arinze, Nwadiogo Chisom; Ogbonnaya, Chisom Esther; Ndukaihe, Izuchukwu L. G.; Dalgar, Ilker; Akkas, Handan; Macapagal, Paulo Manuel; Lewis, Savannah; Metin-Orta, Irem; Foroni, Francesco; Willis, Megan; Santos, Anabela Caetano; Mokady, Aviv; Reggev, Niv; Kurfali, Merve A.; Vasilev, Martin R.; Nock, Nora L.; Parzuchowski, Michal; Espinoza Barr铆a, Mauricio F.; Vranka, Marek; Kohlov谩, Mark茅ta Braun; Ropovik, Ivan; Harutyunyan, Mikayel; Wang, Chunhui; Yao, Elvin; Becker, Maja; Manunta, Efisio; Kaminski, Gwenael; Boudesseu, Jordane; Marko, Dafne; Evans, Kortnee; Lewis, David M. G.; Findor, Andrej; Landry, Anais Thibault; Aruta, John Jamir Benzon; Ortiz, Manuel S.; Vally, Zahir; Pronizius, Ekaterina; Voracek, Martin; Lamm, Claus; Grinberg, Maurice; Li, Ranran; Valentova, Jaroslava Varella; Mioni, Giovanna; Cellini, Nicola; Chen, Sau-Chin; Zickfeld, Janis; Moon, Karis; Azab, Habiba; Levy, Neil; Karababa, Alper; Beaudry, Jennifer L.; Boucher, Leanne; Collins, W. Matthew; Todsen, Anna Louise; van Schie, Kevin; Vintr, J谩chym; Bavolar, Jozef; Kaliska, Lada; Kri啪ani膰, Valerija; Samojlenko, Lara; Pourafshari, Razieh; Geiger, Sandra J.; Beitner, Julia; Warmelink, Lara; Ross, Robert M.; Stephen, Ian D.; Hostler, Thomas J.; Azouaghe, Soufian; McCarthy, Randy; Szala, Anna; Grano, Caterina; Solorzano, Claudio Singh; Anjum, Gulnaz; Jimenez-Leal, William; Bradford, Maria; P茅rez, Laura Calder贸n; Cruz V谩squez, Julio E.; Galindo-Caballero, Oscar J.; Vargas-Nieto, Juan Camilo; K谩cha, Ond艡ej; Arvanitis, Alexios; Xiao, Qinyu; C谩rcamo, Rodrigo; Zorjan, Sa拧a; Tajchman, Zuzanna; Vilares, Iris; Pavlacic, Jeffrey M.; Kunst, Jonas R.; Tamnes, Christian K.; von Bastian, Claudia C.; Atari, Mohammad; Sharifian, MohammadHasan; Hricova, Monika; Ka膷m谩r, Pavol; Schr枚tter, Jana; Rahal, Rima-Maria; Cohen, Noga; FatahModares, Saeideh; Zrimsek, Miha; Zakharov, Ilya; Koehn, Monica A.; Esteban-Serna, Celia; Calin-Jageman, Robert J.; Krafnick, Anthony J.; 艩trukelj, Eva; Isager, Peder Mortvedt; Urban, Jan; Silva, Jaime R.; Marton膷ik, Marcel; O膷ovaj, Sanja Bati膰; 艩akan, Du拧ana; Kuzminska, Anna O.; Djordjevic, Jasna Milosevic; Almeida, In锚s A. T.; Ferreira, Ana; Lazarevic, Ljiljana B.; Manley, Harry; Ricaurte, Danilo Zambrano; Monteiro, Renan P.; Etabari, Zahra; Musser, Erica; Dunleavy, Daniel; Chou, Weilun; Godbersen, Hendrik; Ruiz-Fern谩ndez, Susana; Reeck, Crystal; Batres, Carlota; Kirgizova, Komila; Muminov, Abdumalik; Azevedo, Flavio; Alvarez, Daniela Serrato; Butt, Muhammad Mussaffa; Lee, Jeong Min; Chen, Zhang; Verbruggen, Frederick; Ziano, Ignazio; T眉mer, Murat; Charyate, Abdelilah C. A.; Dubrov, Dmitrii; Tejada Rivera, Mar铆a del Carmen M. C.; Aberson, Christopher; P谩lfi, Bence; Maldonado, M贸nica Alarc贸n; Hubena, Barbora; Sacakli, Asli; Ceary, Chris D.; Richard, Karley L.; Singer, Gage; Perillo, Jennifer T.; Ballantyne, Tonia; Cyrus-Lai, Wilson; Fedotov, Maksim; Du, Hongfei; Wielgus, Magdalena; Pit, Ilse L.; Hru拧ka, Matej; Sousa, Daniela; Aczel, Balazs; Hajdu, Nandor; Szaszi, Barnabas; Adamus, Sylwia; Barzykowski, Krystian; Micheli, Leticia; Schmidt, Nadya-Daniela; Zsido, Andras N.; Paruzel-Czachura, Mariola; Muda, Rafa艂; Bialek, Michal; Kowal, Marta; Sorokowska, Agnieszka; Misiak, Michal; Mola, D茅bora; Ortiz, Mar铆a Victoria; Correa, Pablo Sebasti谩n; Belaus, Anabel; Muchembled, Fany; Ribeiro, Rafael R.; Arriaga, Patricia; Oliveira, Raquel; Vaughn, Leigh Ann; Szwed, Paulina; Kossowska, Ma艂gorzata; Czarnek, Gabriela; Kieli艅ska, Julita; Antazo, Benedict; Betlehem, Ruben; Stieger, Stefan; Nilsonne, Gustav; Simonovic, Nicolle; Taber, Jennifer; Gourdon-Kanhukamwe, Am茅lie; Domurat, Artur; Ihaya, Keiko; Yamada, Yuki; Urooj, Anum; Gill, Tripat; 膶adek, Martin; Bylinina, Lisa; Messerschmidt, Johanna; Kurfal谋, Murathan; Adetula, Adeyemi; Baklanova, Ekaterina; Albayrak-Aydemir, Nihan; Kappes, Heather B.; Gjoneska, Biljana; House, Thea; Jones, Marc V.; Berkessel, Jana B.; Chopik, William J.; 脟oksan, Sami; Seehuus, Martin; Khaoudi, Ahmed; Bokkour, Ahmed; El Arabi, Kanza Ait; Djamai, Ikhlas; Iyer, Aishwarya; Parashar, Neha; Adiguzel, Arca; Kocalar, Halil Emre; Bundt, Carsten; Norton, James O.; Papadatou-Pastou, Marietta; De la Rosa-Gomez, Anabel; Ankushev, Vladislav; Bogatyreva, Natalia; Grigoryev, Dmitry; Ivanov, Aleksandr; Prusova, Irina; Romanova, Marina; Sarieva, Irena; Terskova, Maria; Hristova, Evgeniya; Kadreva, Veselina Hristova; Janak, Allison; Schei, Vidar; Sverdrup, Therese E.; Askelund, Adrian Dahl; Pineda, Lina Maria Sanabria; Krupi膰, Dajana; Levitan, Carmel A.; Johannes, Niklas; Ouherrou, Nihal; Say, Nicolas; Sinkolova, Sladjana; Janji膰, Kristina; Stojanovska, Marija; Stojanovska, Dragana; Khosla, Meetu; Thomas, Andrew G.; Kung, Franki Y. H.; Bijlstra, Gijsbert; Mosannenzadeh, Farnaz; Balci, Busra Bahar; Reips, Ulf-Dietrich; Baskin, Ernest; Ishkhanyan, Byurakn; Czamanski-Cohen, Johanna; Dixson, Barnaby James Wyld; Moreau, David; Sutherland, Clare A. M.; Chuan-Peng, Hu; Noone, Chris; Flowe, Heather; Anne, Michele; Janssen, Steve M. J.; Topor, Marta; Majeed, Nadyanna M.; Kunisato, Yoshihiko; Yu, Karen; Daches, Shimrit; Hartanto, Andree; Vdovic, Milica; Anton-Boicuk, Lisa; Forbes, Paul A. G.; Kamburidis, Julia; Marinova, Evelina; Nedelcheva-Datsova, Mina; Rachev, Nikolay R.; Stoyanova, Alina; Schmidt, Kathleen; Suchow, Jordan W.; Koptjevskaja-Tamm, Maria; Jerns盲ther, Teodor; Olofsson, Jonas K.; Bialobrzeska, Olga; Marszalek, Magdalena; Tatachari, Srinivasan; Afhami, Reza; Law, Wilbert; Antfolk, Jan; 沤uro, Barbara; Van Doren, Natalia; Soto, Jose A.; Searston, Rachel; Miranda, Jacob; Damnjanovi膰, Kaja; Yeung, Siu Kit; Krupi膰, Dino; Hoyer, Karlijn; Jaeger, Bastian; Ren, Dongning; Pfuhl, Gerit; Klevjer, Kristoffer; Corral-Fr铆as, Nadia S.; Frias-Armenta, Martha; Lucas, Marc Y.; Torres, Adriana Olaya; Toro, M贸nica; Delgado, Lady Grey Javela; Vega, Diego; Solas, Sara 脕lvarez; Vilar, Roosevelt; Massoni, S茅bastien; Frizzo, Thomas; Bran, Alexandre; Vaidis, David C.; Vieira, Luc; Paris, Bastien; Capizzi, Mariagrazia; Coelho, Gabriel Lins de Holanda; Greenburgh, Anna; Whitt, Cassie M.; Tullett, Alexa M.; Du, Xinkai; Volz, Leonhard; Bosma, Minke Jasmijn; Karaarslan, Cemre; Sar谋o臒uz, Eyl眉l; Allred, Tara Bulut; Korbmacher, Max; Colloff, Melissa F.; Lima, Tiago J. S.; Ribeiro, Matheus Fernando Felix; Verharen, Jeroen P. H.; Karekla, Maria; Karashiali, Christiana; Sunami, Naoyuki; Jaremka, Lisa M.; Storage, Daniel; Habib, Sumaiya; Studzinska, Anna; Hanel, Paul H. P.; Holford, Dawn Liu; Sirota, Miroslav; Wolfe, Kelly; Chiu, Faith; Theodoropoulou, Andriana; Ahn, El Rim; Lin, Yijun; Westgate, Erin C.; Brohmer, Hilmar; Hofer, Gabriela; Dujols, Olivier; Vezirian, Kevin; Feldman, Gilad; Travaglino, Giovanni A.; Ahmed, Afroja; Li, Manyu; Bosch, Jasmijn; Torunsky, Nathan; Bai, Hui; Manavalan, Mathi; Song, Xin; Walczak, Radoslaw B.; Zdybek, Przemys艂aw; Friedemann, Maja; Rosa, Anna Dalla; Kozma, Luca; Alves, Sara G.; Lins, Samuel; Pinto, Isabel R.; Correia, Rita C.; Babin膷谩k, Peter; Banik, Gabriel; Rojas-Berscia, Luis Miguel; Varella, Marco A. C.; Uttley, Jim; Beshears, Julie E.; Thommesen, Katrine Krabbe; Behzadnia, Behzad; Geniole, Shawn N.; Silan, Miguel A.; Maturan, Princess Lovella G.; Vilsmeier, Johannes K.; Tran, Ulrich S.; Izquierdo, Sara Morales; Mensink, Michael C.; Sorokowski, Piotr; Groyecka-Bernard, Agata; Radtke, Theda; Adoric, Vera Cubela; Carpentier, Joelle; 脰zdo臒ru, Asil Ali; Joy-Gaba, Jennifer A.; Hedgebeth, Mattie V.; Ishii, Tatsunori; Wichman, Aaron L.; R枚er, Jan Philipp; Ostermann, Thomas; Davis, William E.; Suter, Lilian; Papachristopoulos, Konstantinos; Zabel, Chelsea; Onie, Sandersan; Ebersole, Charles R.; Chartier, Christopher R.; Mallik, Peter R.; Urry, Heather L.; Buchanan, Erin M.; Coles, Nicholas A.; Primbs, Maximilian A.; Basnight-Brown, Dana M.; IJzerman, Hans; Forscher, Patrick S.; Moshontz, Hannah</t>
-  </si>
-  <si>
-    <t>A multi-country test of brief reappraisal interventions on emotions during the COVID-19 pandemic</t>
-  </si>
-  <si>
-    <t>Reappraisal, Emotions, COVID-19, Multi-country, Interventions</t>
-  </si>
-  <si>
-    <t>Wasiel, Arkadiusz; G贸rski, Maciej R.; Bond, Michael Harris; Yeung, Victoria Wai Lan; Akaliyski, Plamen; Akello, Grace; Park, Joonha; Joshanloo, Mohsen; Sokolov, Boris; Hussain, M. Azhar; Li, Liman Man Wai; Olechowski, Mateusz; Vignoles, Vivian L.; Guemaz, Farida; Boussena, Mahmoud; Rabby, Md. Reza-A; Okvitawanli, Ayu; My艣li艅ska-Szarek, Katarzyna; Haas, Brian W.; S谩nchez-Rodr铆guez, 脕ngel; Vlasenko, Olha; Lun, Vivian Miu-Chi; Aminnuddin, Nur Amali; I艧谋k, 陌dil; Barry, Oumar; F眉l枚p, M谩rta; Igbokwe, David; Adamovic, Mladen; Gar冒arsd贸ttir, Ragna Benedikta; Soboleva, Natalia; Teyssier, Julien; Gl眉ckstad, Fumiko Kano; Samekin, Adil; Akotia, Charity; Al-Zoubi, Marwan; Andrade, Laura; Ani膰, Petra; Bakyono-Nabaloum, Rasmata; Baltin, Arno; Costin, Vlad; Denoux, Patrick; Espinosa, Alejandra Dom铆nguez; Espinosa, Agustin; Gamsakhurdia, Vladimer; Garvanova, Magdalena; Gavreliuc, Alin; Gjoneska, Biljana; Igou, Eric Raymond; Iqbal, Naved; Iter, Nuha; Kascakova, Natalia; Kazimzade, Elmina; Kluzowicz, Maria; Kocimska-Bortnowska, Agata; Kronberger, Nicole; Lauri, Mary Anne; Lee, Hannah; Malyonova, Arina; Maricchiolo, Fridanna; Mohammed, Linda; Mokadem, Fatma; Mosanya, Magdalena; Mosca, Oriana; Murdock, Elke; Nader, Martin; Nowak, Karolina; Ochoa, Danielle; Pavlovi膰, Zoran; 艩olcov谩, Iva Pol谩膷kov谩; Purc, Ewelina; Rizwan, Muhammad; Rocha, Ana Maria; Selim, Heyla; Sobhie, Rosita; Streng, Moritz; Sun, Chien-Ru; T酶nnessen, Morten; Torres, Claudio; Tr脿, Ki峄乽 Th峄?Thanh; Turja膷anin, Vladimir; van Tilburg, Wijnand; Vauclair, Christin-Melanie; Vergara-Morales, Jorge; Xing, Cai; Yakhlef, Belkacem; Yang, Jae-Won; Yau, Eric Kenson; Yeung, June Chun; Zelenski, John; Krys, Kuba</t>
-  </si>
-  <si>
-    <t>22Examining the connection between position-based power and social status across 70 cultures</t>
-  </si>
-  <si>
-    <t>Power, Social Status, Culture, Self-Orientation, Other-Orientation</t>
-  </si>
-  <si>
-    <t>Yik, Michelle; Mues, Chiel; Sze, Irene N. L.; Kuppens, Peter; Tuerlinckx, Francis; De Roover, Kim; Kwok, Felity H. C.; Schwartz, Shalom H.; Abu-Hilal, Maher; Adebayo, Damilola Fisayo; Aguilar, Pilar; Al-Bahrani, Muna; Anderson, Marc H.; Andrade, Laura; Bratko, Denis; Bushina, Ekaterina; Choi, Jeong Won; Cieciuch, Jan; Dru, Vincent; Evers, Uwana; Fischer, Ronald; Florez, Ivonne Andrea; Gar冒arsd贸ttir, Ragna B.; Gari, Aikaterini; Graf, Sylvie; Halama, Peter; Halberstadt, Jamin; Halim, Magdalena S.; Heilman, Renata M.; H艡eb铆膷kov谩, Martina; Karl, Johannes Alfons; Kne啪evi膰, Goran; Koh煤t, Michal; Kolnes, Martin; Lazarevi膰, Ljiljana B.; Lebedeva, Nadezhda; Lee, Julie; Lee, Young-Ho; Liu, Chunquan; Mannerstr枚m, Rasmus; Maru拧i膰, Iris; Nansubuga, Florence; Ojedokun, Oluyinka; Park, Joonha; Platt, Tracey; Proyer, Ren茅 T.; Realo, Anu; Rolland, Jean-Pierre; Ruch, Willibald; Ruiz, Desiree; Sortheix, Florencia M.; Stahlmann, Alexander Georg; Stojanov, Ana; Strus, W艂odzimierz; Tamir, Maya; Torres, Cl谩udio; Trujillo, Angela; Truong, Thi Khanh Ha; Utsugi, Akira; Vecchione, Michele; Wang, Lei; Russell, James A.</t>
-  </si>
-  <si>
-    <t>22On the relationship between valence and arousal in samples across the globe</t>
-  </si>
-  <si>
-    <t>valence, arousal, subjective experience, structure of affect, culture</t>
-  </si>
-  <si>
-    <t>Zickfeld, Janis H.; van de Ven, Niels; Pich, Olivia; Schubert, Thomas W.; Berkessel, Jana B.; Pizarro, Jos茅 J.; Bhushan, Braj; Mateo, Nino Jose; Barbosa, Sergio; Sharman, Leah; K枚k枚nyei, Gy枚ngyi; Schrover, Elke; Kardum, Igor; Aruta, John Jamir Benzon; Lazarevic, Ljiljana B.; Escobar, Mar铆a Josefina; Stadel, Marie; Arriaga, Patr铆cia; Dodaj, Arta; Shankland, Rebecca; Majeed, Nadyanna M.; Li, Yansong; Lekkou, Eleimonitria; Hartanto, Andree; 脰zdo臒ru, Asil A.; Vaughn, Leigh Ann; del Carmen Espinoza, Maria; Caballero, Amparo; Kolen, Anouk; Karsten, Julie; Manley, Harry; Maeura, Nao; E艧kisu, Mustafa; Shani, Yaniv; Chittham, Phakkanun; Ferreira, Diogo; Bavolar, Jozef; Konova, Irina; Sato, Wataru; Morvinski, Coby; Carrera, Pilar; Villar, Sergio; Ibanez, Agustin; Hareli, Shlomo; Garcia, Adolfo M.; Kremer, Inbal; G枚tz, Friedrich M.; Schwerdtfeger, Andreas; Estrada-Mejia, Catalina; Nakayama, Masataka; Ng, Wee Qin; Sesar, Kristina; Orjiakor, Charles T.; Dumont, Kitty; Allred, Tara Bulut; Gra膷anin, Asmir; Rentfrow, Peter J.; Sch枚nefeld, Victoria; Vally, Zahir; Barzykowski, Krystian; Peltola, Henna-Riikka; Tcherkassof, Anna; Haque, Shamsul; 艢mieja, Magdalena; Su-May, Terri Tan; IJzerman, Hans; Vatakis, Argiro; Ong, Chew Wei; Choi, Eunsoo; Schorch, Sebastian L.; P谩ez, Dar铆o; Malik, Sadia; Ka膷m谩r, Pavol; Bobowik, Magdalena; Jose, Paul; Vuoskoski, Jonna K.; Basabe, Nekane; Do臒an, U臒ur; Ebert, Tobias; Uchida, Yukiko; Zheng, Michelle Xue; Mefoh, Philip; 艩ebe艌a, Ren茅; Stanke, Franziska A.; Ballada, Christine Joy; Blaut, Agata; Wu, Yang; Daniels, Judith K.; Kocsel, Nat谩lia; Burak, Elif Gizem Demirag; Balt, Nina F.; Vanman, Eric; Stewart, Suzanne L. K.; Verschuere, Bruno; Sikka, Pilleriin; Boudesseul, Jordane; Martins, Diogo; Nussinson, Ravit; Ito, Kenichi; Mentser, Sari; 脟olak, Tu臒ba Seda; Martinez-Zelaya, Gonzalo; Vingerhoets, Ad</t>
-  </si>
-  <si>
-    <t>Tears evoke the intention to offer social support: A systematic investigation of the interpersonal effects of emotional crying across 41 countries</t>
-  </si>
-  <si>
-    <t>Emotional crying Emotional tears Attachment Cross-cultural Social support</t>
-  </si>
-  <si>
-    <t>Anger and disgust shape judgments of social sanctions across cultures, especially in high individual autonomy societies</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>COVID-19, social attitudes, identity, moral beliefs, compliance behaviours</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>thinking, individual differences, cultural differences, replication</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Moral judgement, personal force effect, replication, Cultural universality, Trolley dilemma</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Semantic Priming Effect, Cross-linguistic variability, Response latency, Semantic Similarity, Registered Report</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>The Psychological Science Accelerator's COVID-19 rapid-response dataset</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gaze Following, Bilingual Infants, Monolingual Infants, multi-laboratory study, Developmental Trajectory</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>cross-lingual research, language comprehension, mental rotation, mental simulation</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Facial feedback hypothesis, Facial mimicry task, Voluntary facial action task, Pen-in-mouth task, Emotional experience</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Trust in scientists, Science-related populism, Social dominance orientation, Political orientation, Role of scientists in society</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Experimental Philosophy, Reproducibility, Replication, Effect Size, representative sample</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>climate change, behavioral interventions, global study, beliefs, policy support</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>scientific consensus, climate change, misperceptions, climate change beliefs, worry</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>remote web-based eye-tracking, WebGazer, toddlers, anticipatory looking, validation</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Modernization, collectivism, gender equality, love experiences, Triangular Theory of Love</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Group meta-perceptions, Political polarization, Replication, Intergroup relations, Cross-cultural generalizability</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>temporal discounting, globalizability, intertemporal choice, economic inequality, financial circumstances</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>brain-age, Latin America and Caribbean countries (LAC), functional magnetic resonance imaging (fMRI), electroencephalography (EEG), Alzheimer disease</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>valence–dominance model, valence, dominance, faces, social judgements</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Conspiracy mentality, Political orientation, Cross-national, Quadratic relationship, Political control deprivation</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Data from the Human Penguin Project, a cross-national dataset testing social thermoregulation principles</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>social thermoregulation, social networks, geographical, climate, cross-national dataset</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dataset, Loss-Gain Framing, Cognitive Reappraisal, Self-Determination Theory, COVID-19</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sustainable Development Goals, Human Development Index, Environment Performance Index, Students,  Global Survey</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Brain clocks capture diversity and disparities in aging and dementia across geographically diverse populations</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Statistics; mathematics; anxiety; education; jangle fallacy</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Elb忙k, Christian T.; Mitkidis, Panagiotis; Aar酶e, Lene; Otterbring, Tobias</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Statistics, mathematics, anxiety, education, jangle fallacy</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1690,7 +1683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A00A682E-359B-40D2-AA62-2EFDEBBAE5C0}">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="8.8984375" bestFit="1" customWidth="1"/>
@@ -1720,7 +1713,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
@@ -1751,7 +1744,7 @@
         <v>10</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.5">
@@ -1765,7 +1758,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -1793,7 +1786,7 @@
         <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.5">
@@ -1804,10 +1797,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -1821,7 +1814,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -1849,7 +1842,7 @@
         <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -1863,7 +1856,7 @@
         <v>27</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.5">
@@ -1877,7 +1870,7 @@
         <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.5">
@@ -1891,7 +1884,7 @@
         <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.5">
@@ -1905,7 +1898,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.5">
@@ -1983,7 +1976,7 @@
         <v>99000020</v>
       </c>
       <c r="B21" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="C21" t="s">
         <v>49</v>
@@ -2168,10 +2161,10 @@
         <v>87</v>
       </c>
       <c r="C34" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.5">
@@ -2185,7 +2178,7 @@
         <v>89</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -2213,7 +2206,7 @@
         <v>94</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -2269,7 +2262,7 @@
         <v>105</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="42" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
@@ -2406,10 +2399,10 @@
         <v>133</v>
       </c>
       <c r="C51" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.5">
@@ -2493,7 +2486,7 @@
         <v>150</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.5">
@@ -2507,7 +2500,7 @@
         <v>152</v>
       </c>
       <c r="D58" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.5">
@@ -2520,8 +2513,8 @@
       <c r="C59" t="s">
         <v>154</v>
       </c>
-      <c r="D59" t="s">
-        <v>155</v>
+      <c r="D59" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.5">
@@ -2529,13 +2522,13 @@
         <v>99000059</v>
       </c>
       <c r="B60" t="s">
+        <v>155</v>
+      </c>
+      <c r="C60" t="s">
         <v>156</v>
       </c>
-      <c r="C60" t="s">
-        <v>157</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>210</v>
+      <c r="D60" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.5">
@@ -2543,31 +2536,31 @@
         <v>99000060</v>
       </c>
       <c r="B61" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" t="s">
         <v>158</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>159</v>
       </c>
-      <c r="D61" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.5">
+    </row>
+    <row r="62" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A62">
         <v>99000061</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D62" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A63" s="2">
+      <c r="A63">
         <v>99000062</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -2581,59 +2574,59 @@
       </c>
     </row>
     <row r="64" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A64" s="2">
+      <c r="A64">
         <v>99000063</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A65">
+        <v>99000064</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="C65" s="3" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A65" s="2">
-        <v>99000064</v>
-      </c>
-      <c r="B65" s="2" t="s">
+      <c r="D65" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C65" s="2" t="s">
+    </row>
+    <row r="66" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A66">
+        <v>99000065</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A66" s="3">
-        <v>99000065</v>
-      </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D66" s="3" t="s">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.5">
+      <c r="A67">
+        <v>99000066</v>
+      </c>
+      <c r="B67" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A67" s="3">
-        <v>99000066</v>
-      </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" t="s">
         <v>174</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" t="s">
         <v>175</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.5">
@@ -2641,13 +2634,13 @@
         <v>99000067</v>
       </c>
       <c r="B68" t="s">
+        <v>176</v>
+      </c>
+      <c r="C68" t="s">
         <v>177</v>
       </c>
-      <c r="C68" t="s">
-        <v>178</v>
-      </c>
-      <c r="D68" t="s">
-        <v>179</v>
+      <c r="D68" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.5">
@@ -2655,13 +2648,13 @@
         <v>99000068</v>
       </c>
       <c r="B69" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C69" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.5">
@@ -2669,69 +2662,55 @@
         <v>99000069</v>
       </c>
       <c r="B70" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" t="s">
+        <v>181</v>
+      </c>
+      <c r="D70" t="s">
         <v>182</v>
       </c>
-      <c r="C70" t="s">
-        <v>183</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.5">
+    </row>
+    <row r="71" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
       <c r="A71">
         <v>99000070</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D71" t="s">
+    </row>
+    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A72">
+        <v>99000071</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A72" s="2">
-        <v>99000071</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D72" s="2" t="s">
+    </row>
+    <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
+      <c r="A73">
+        <v>99000072</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A73" s="2">
-        <v>99000072</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="D73" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.5">
-      <c r="A74" s="2">
-        <v>99000073</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
